--- a/cet4/result/60_谍战女神_暗夜玫瑰的秘密/60_谍战女神_暗夜玫瑰的秘密_学习版.xlsx
+++ b/cet4/result/60_谍战女神_暗夜玫瑰的秘密/60_谍战女神_暗夜玫瑰的秘密_学习版.xlsx
@@ -397,885 +397,717 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>midnight</v>
       </c>
       <c r="B2" t="str">
-        <v>midnight</v>
+        <v>/ˈmɪdnaɪt/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>午夜</v>
       </c>
-      <c r="D2" t="str">
-        <v>midnight(午夜)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>steamer</v>
       </c>
       <c r="B3" t="str">
-        <v>steamer</v>
+        <v>/ˈstiːmər/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>轮船</v>
       </c>
-      <c r="D3" t="str">
-        <v>steamer(轮船)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>smoke</v>
       </c>
       <c r="B4" t="str">
-        <v>smoke</v>
+        <v>/smoʊk/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D4" t="str">
         <v>烟雾</v>
       </c>
-      <c r="D4" t="str">
-        <v>smoke(烟雾)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>candidate</v>
       </c>
       <c r="B5" t="str">
-        <v>candidate</v>
+        <v>/ˈkændɪdət/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>候选人</v>
       </c>
-      <c r="D5" t="str">
-        <v>candidate(候选人)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>operation</v>
       </c>
       <c r="B6" t="str">
-        <v>operation</v>
+        <v>/ˌɑːpəˈreɪʃn/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>行动</v>
       </c>
-      <c r="D6" t="str">
-        <v>operation(行动)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>European</v>
       </c>
       <c r="B7" t="str">
-        <v>European</v>
+        <v>/ˌjʊrəˈpiːən/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>欧洲</v>
       </c>
-      <c r="D7" t="str">
-        <v>European(欧洲)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>international</v>
       </c>
       <c r="B8" t="str">
-        <v>international</v>
+        <v>/ˌɪntərˈnæʃnəl/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>国际</v>
       </c>
-      <c r="D8" t="str">
-        <v>international(国际)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>musical</v>
       </c>
       <c r="B9" t="str">
-        <v>musical</v>
+        <v>/ˈmjuːzɪkl/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>音乐</v>
       </c>
-      <c r="D9" t="str">
-        <v>musical(音乐)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>tennis</v>
       </c>
       <c r="B10" t="str">
-        <v>tennis</v>
+        <v>/ˈtenɪs/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>网球</v>
       </c>
-      <c r="D10" t="str">
-        <v>tennis(网球)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>submarine</v>
       </c>
       <c r="B11" t="str">
-        <v>submarine</v>
+        <v>/ˌsʌbməˈriːn/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>潜艇</v>
       </c>
-      <c r="D11" t="str">
-        <v>submarine(潜艇)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>equipment</v>
       </c>
       <c r="B12" t="str">
-        <v>equipment</v>
+        <v>/ɪˈkwɪpmənt/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>装备</v>
       </c>
-      <c r="D12" t="str">
-        <v>equipment(装备)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>diary</v>
       </c>
       <c r="B13" t="str">
-        <v>diary</v>
+        <v>/ˈdaɪəri/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>日记</v>
       </c>
-      <c r="D13" t="str">
-        <v>diary(日记)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>jewel</v>
       </c>
       <c r="B14" t="str">
-        <v>jewel</v>
+        <v>/ˈdʒuːəl/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D14" t="str">
         <v>珠宝</v>
       </c>
-      <c r="D14" t="str">
-        <v>jewel(珠宝)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>gloomy</v>
       </c>
       <c r="B15" t="str">
-        <v>gloomy</v>
+        <v>/ˈɡluːmi/</v>
       </c>
       <c r="C15" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>阴暗</v>
       </c>
-      <c r="D15" t="str">
-        <v>gloomy(阴暗)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>cousin</v>
       </c>
       <c r="B16" t="str">
-        <v>cousin</v>
+        <v>/ˈkʌzn/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>表兄</v>
       </c>
-      <c r="D16" t="str">
-        <v>cousin(表兄)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>condition</v>
       </c>
       <c r="B17" t="str">
-        <v>condition</v>
+        <v>/kənˈdɪʃn/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D17" t="str">
         <v>情况</v>
       </c>
-      <c r="D17" t="str">
-        <v>condition(情况)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>point</v>
       </c>
       <c r="B18" t="str">
-        <v>point</v>
+        <v>/pɔɪnt/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>要点</v>
       </c>
-      <c r="D18" t="str">
-        <v>point(要点)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>unfortunate</v>
       </c>
       <c r="B19" t="str">
-        <v>unfortunate</v>
+        <v>/ʌnˈfɔːrtʃənət/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>不幸的</v>
       </c>
-      <c r="D19" t="str">
-        <v>unfortunate(不幸的)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>niece</v>
       </c>
       <c r="B20" t="str">
-        <v>niece</v>
+        <v>/niːs/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>侄女</v>
       </c>
-      <c r="D20" t="str">
-        <v>niece(侄女)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>attentive</v>
       </c>
       <c r="B21" t="str">
-        <v>attentive</v>
+        <v>/əˈtentɪv/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>注意的</v>
       </c>
-      <c r="D21" t="str">
-        <v>attentive(注意的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>envy</v>
       </c>
       <c r="B22" t="str">
-        <v>envy</v>
+        <v>/ˈenvi/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>嫉妒</v>
       </c>
-      <c r="D22" t="str">
-        <v>envy(嫉妒)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>gross</v>
       </c>
       <c r="B23" t="str">
-        <v>gross</v>
+        <v>/ɡroʊs/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>粗俗的</v>
       </c>
-      <c r="D23" t="str">
-        <v>gross(粗俗的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>one</v>
       </c>
       <c r="B24" t="str">
-        <v>one</v>
+        <v>/wʌn/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./adj./pron./num.</v>
+      </c>
+      <c r="D24" t="str">
         <v>一个</v>
       </c>
-      <c r="D24" t="str">
-        <v>one(一个)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>complicated</v>
       </c>
       <c r="B25" t="str">
-        <v>complicated</v>
+        <v>/ˈkɑːmplɪkeɪtɪd/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>复杂</v>
       </c>
-      <c r="D25" t="str">
-        <v>complicated(复杂)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>basically</v>
       </c>
       <c r="B26" t="str">
-        <v>basically</v>
+        <v>/ˈbeɪsɪkli/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D26" t="str">
         <v>基本上</v>
       </c>
-      <c r="D26" t="str">
-        <v>basically(基本上)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>fluid</v>
       </c>
       <c r="B27" t="str">
-        <v>fluid</v>
+        <v>/ˈfluːɪd/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>液体</v>
       </c>
-      <c r="D27" t="str">
-        <v>fluid(液体)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>hungry</v>
       </c>
       <c r="B28" t="str">
-        <v>hungry</v>
+        <v>/ˈhʌŋɡri/</v>
       </c>
       <c r="C28" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>饥饿</v>
       </c>
-      <c r="D28" t="str">
-        <v>hungry(饥饿)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>remote</v>
       </c>
       <c r="B29" t="str">
-        <v>remote</v>
+        <v>/rɪˈmoʊt/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>远程</v>
       </c>
-      <c r="D29" t="str">
-        <v>remote(远程)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>careless</v>
       </c>
       <c r="B30" t="str">
-        <v>careless</v>
+        <v>/ˈkerləs/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D30" t="str">
         <v>粗心</v>
       </c>
-      <c r="D30" t="str">
-        <v>careless(粗心)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>brake</v>
       </c>
       <c r="B31" t="str">
-        <v>brake</v>
+        <v>/breɪk/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D31" t="str">
         <v>刹车</v>
       </c>
-      <c r="D31" t="str">
-        <v>brake(刹车)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>rescue</v>
       </c>
       <c r="B32" t="str">
-        <v>rescue</v>
+        <v>/ˈreskjuː/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D32" t="str">
         <v>营救</v>
       </c>
-      <c r="D32" t="str">
-        <v>rescue(营救)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>telegraph</v>
       </c>
       <c r="B33" t="str">
-        <v>gloomy</v>
+        <v>/ˈtelɪɡræf/</v>
       </c>
       <c r="C33" t="str">
-        <v>黑暗</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>gloomy(黑暗)📢</v>
+        <v>电报</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>fist</v>
       </c>
       <c r="B34" t="str">
-        <v>unfortunate</v>
+        <v>/fɪst/</v>
       </c>
       <c r="C34" t="str">
-        <v>不幸</v>
+        <v>n./vt.</v>
       </c>
       <c r="D34" t="str">
-        <v>unfortunate(不幸)📢</v>
+        <v>拳头</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>accompany</v>
       </c>
       <c r="B35" t="str">
-        <v>telegraph</v>
+        <v>/əˈkʌmpəni/</v>
       </c>
       <c r="C35" t="str">
-        <v>电报</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>telegraph(电报)📢</v>
+        <v>陪伴</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>shield</v>
       </c>
       <c r="B36" t="str">
-        <v>fist</v>
+        <v>/ʃiːld/</v>
       </c>
       <c r="C36" t="str">
-        <v>拳头</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>fist(拳头)📢</v>
+        <v>盾牌</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>airline</v>
       </c>
       <c r="B37" t="str">
-        <v>accompany</v>
+        <v>/ˈerlaɪn/</v>
       </c>
       <c r="C37" t="str">
-        <v>陪伴</v>
+        <v>n./adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>accompany(陪伴)📢</v>
+        <v>航空公司</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>soak</v>
       </c>
       <c r="B38" t="str">
-        <v>shield</v>
+        <v>/soʊk/</v>
       </c>
       <c r="C38" t="str">
-        <v>盾牌</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>shield(盾牌)📢</v>
+        <v>浸透</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>towel</v>
       </c>
       <c r="B39" t="str">
-        <v>remote</v>
+        <v>/ˈtaʊəl/</v>
       </c>
       <c r="C39" t="str">
-        <v>偏僻的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>remote(偏僻的)📢</v>
+        <v>毛巾</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>fulfil</v>
       </c>
       <c r="B40" t="str">
-        <v>airline</v>
+        <v>/fʊlˈfɪl/</v>
       </c>
       <c r="C40" t="str">
-        <v>航空公司</v>
+        <v>vt.</v>
       </c>
       <c r="D40" t="str">
-        <v>airline(航空公司)📢</v>
+        <v>完成</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>fruitful</v>
       </c>
       <c r="B41" t="str">
-        <v>submarine</v>
+        <v>/ˈfruːtfl/</v>
       </c>
       <c r="C41" t="str">
-        <v>潜水</v>
+        <v>adj.</v>
       </c>
       <c r="D41" t="str">
-        <v>submarine(潜水)📢</v>
+        <v>富有成效的</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>found</v>
       </c>
       <c r="B42" t="str">
-        <v>soak</v>
+        <v>/faʊnd/</v>
       </c>
       <c r="C42" t="str">
-        <v>浸透</v>
+        <v>vt./v.</v>
       </c>
       <c r="D42" t="str">
-        <v>soak(浸透)📢</v>
+        <v>建立</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>difference</v>
       </c>
       <c r="B43" t="str">
-        <v>towel</v>
+        <v>/ˈdɪfrəns/</v>
       </c>
       <c r="C43" t="str">
-        <v>毛巾</v>
+        <v>n.</v>
       </c>
       <c r="D43" t="str">
-        <v>towel(毛巾)📢</v>
+        <v>不同</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>export</v>
       </c>
       <c r="B44" t="str">
-        <v>fulfil</v>
+        <v>/ˈekspɔːrt/</v>
       </c>
       <c r="C44" t="str">
-        <v>完成</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>fulfil(完成)📢</v>
+        <v>输出</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>reel</v>
       </c>
       <c r="B45" t="str">
-        <v>fruitful</v>
+        <v>/riːl/</v>
       </c>
       <c r="C45" t="str">
-        <v>富有成效的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>fruitful(富有成效的)📢</v>
+        <v>卷轴</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>furnace</v>
       </c>
       <c r="B46" t="str">
-        <v>found</v>
+        <v>/ˈfɜːrnɪs/</v>
       </c>
       <c r="C46" t="str">
-        <v>建立</v>
+        <v>n.</v>
       </c>
       <c r="D46" t="str">
-        <v>found(建立)📢</v>
+        <v>熔炉</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>his</v>
       </c>
       <c r="B47" t="str">
-        <v>European</v>
+        <v>/hɪz,ɪz/</v>
       </c>
       <c r="C47" t="str">
-        <v>欧洲</v>
+        <v>n./pron.</v>
       </c>
       <c r="D47" t="str">
-        <v>European(欧洲)📢</v>
+        <v>他的</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>volume</v>
       </c>
       <c r="B48" t="str">
-        <v>complicated</v>
+        <v>/ˈvɑːljuːm,ˈvɑːljəm/</v>
       </c>
       <c r="C48" t="str">
-        <v>复杂</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>complicated(复杂)📢</v>
+        <v>量</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>gradually</v>
       </c>
       <c r="B49" t="str">
-        <v>difference</v>
+        <v>/ˈɡrædʒuəli/</v>
       </c>
       <c r="C49" t="str">
-        <v>不同</v>
+        <v>v./adv.</v>
       </c>
       <c r="D49" t="str">
-        <v>difference(不同)📢</v>
+        <v>逐渐</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>reduction</v>
       </c>
       <c r="B50" t="str">
-        <v>export</v>
+        <v>/rɪˈdʌkʃn/</v>
       </c>
       <c r="C50" t="str">
-        <v>输出</v>
+        <v>n.</v>
       </c>
       <c r="D50" t="str">
-        <v>export(输出)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>reel</v>
-      </c>
-      <c r="C51" t="str">
-        <v>卷轴</v>
-      </c>
-      <c r="D51" t="str">
-        <v>reel(卷轴)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>rescue</v>
-      </c>
-      <c r="C52" t="str">
-        <v>营救</v>
-      </c>
-      <c r="D52" t="str">
-        <v>rescue(营救)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>furnace</v>
-      </c>
-      <c r="C53" t="str">
-        <v>熔炉</v>
-      </c>
-      <c r="D53" t="str">
-        <v>furnace(熔炉)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>his</v>
-      </c>
-      <c r="C54" t="str">
-        <v>他的</v>
-      </c>
-      <c r="D54" t="str">
-        <v>his(他的)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>candidate</v>
-      </c>
-      <c r="C55" t="str">
-        <v>候选人</v>
-      </c>
-      <c r="D55" t="str">
-        <v>candidate(候选人)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>international</v>
-      </c>
-      <c r="C56" t="str">
-        <v>国际</v>
-      </c>
-      <c r="D56" t="str">
-        <v>international(国际)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>volume</v>
-      </c>
-      <c r="C57" t="str">
-        <v>量</v>
-      </c>
-      <c r="D57" t="str">
-        <v>volume(量)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>gradually</v>
-      </c>
-      <c r="C58" t="str">
-        <v>逐渐</v>
-      </c>
-      <c r="D58" t="str">
-        <v>gradually(逐渐)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>one</v>
-      </c>
-      <c r="C59" t="str">
-        <v>一</v>
-      </c>
-      <c r="D59" t="str">
-        <v>one(一)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>fulfil</v>
-      </c>
-      <c r="C60" t="str">
-        <v>完成</v>
-      </c>
-      <c r="D60" t="str">
-        <v>fulfil(完成)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>equipment</v>
-      </c>
-      <c r="C61" t="str">
-        <v>装备</v>
-      </c>
-      <c r="D61" t="str">
-        <v>equipment(装备)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>reduction</v>
-      </c>
-      <c r="C62" t="str">
         <v>减少</v>
-      </c>
-      <c r="D62" t="str">
-        <v>reduction(减少)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D50"/>
   </ignoredErrors>
 </worksheet>
 </file>